--- a/gu_in/Quest.edf/QuestDesc.xlsx
+++ b/gu_in/Quest.edf/QuestDesc.xlsx
@@ -3,14 +3,27 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CD662-02AD-4F19-BD22-AB1204EA1252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0899A213-4319-4C8E-BDBB-5F1BC69A7729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QDescCli" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/gu_in/Quest.edf/QuestDesc.xlsx
+++ b/gu_in/Quest.edf/QuestDesc.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0899A213-4319-4C8E-BDBB-5F1BC69A7729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44191489-2916-4B2A-814E-A215865E58FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="2312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="2317">
   <si>
     <t>END</t>
   </si>
@@ -8127,6 +8127,21 @@
   </si>
   <si>
     <t>Nexus Daily Quest 5</t>
+  </si>
+  <si>
+    <t>Daily Quest 1</t>
+  </si>
+  <si>
+    <t>Daily Quest 2</t>
+  </si>
+  <si>
+    <t>Daily Quest 3</t>
+  </si>
+  <si>
+    <t>Daily Quest 4</t>
+  </si>
+  <si>
+    <t>Daily Quest 5</t>
   </si>
 </sst>
 </file>
@@ -8170,10 +8185,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8478,7 +8494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4178"/>
+  <dimension ref="A1:D4183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -50267,6 +50283,46 @@
       <c r="C4178" s="2"/>
       <c r="D4178" s="1"/>
     </row>
+    <row r="4179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4179" s="3">
+        <v>4176</v>
+      </c>
+      <c r="B4179" s="3" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4180" s="2">
+        <v>4177</v>
+      </c>
+      <c r="B4180" s="3" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4181" s="3">
+        <v>4178</v>
+      </c>
+      <c r="B4181" s="3" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4182" s="2">
+        <v>4179</v>
+      </c>
+      <c r="B4182" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4183" s="3">
+        <v>4180</v>
+      </c>
+      <c r="B4183" s="3" t="s">
+        <v>2316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
